--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/quant-allocation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E3408E-647F-9E41-82E0-4ADD9AD88C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E30B48C-752E-414B-9234-D9FD628D58AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38240" yWindow="660" windowWidth="38080" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2022" uniqueCount="707">
   <si>
     <t>Ticker</t>
   </si>
@@ -2154,6 +2154,9 @@
   </si>
   <si>
     <t>CH0008742519</t>
+  </si>
+  <si>
+    <t>Schroders Capital Semi-Liquid-Global Private Equity</t>
   </si>
 </sst>
 </file>
@@ -2228,7 +2231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2237,6 +2240,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2542,7 +2546,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F336"/>
+  <dimension ref="A1:F337"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="33.33203125" bestFit="1" customWidth="1"/>
@@ -8989,29 +8993,29 @@
         <v>104</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>692</v>
-      </c>
-      <c r="B323" t="s">
-        <v>676</v>
-      </c>
-      <c r="C323" t="s">
-        <v>676</v>
-      </c>
-      <c r="D323" t="s">
-        <v>677</v>
-      </c>
-      <c r="E323" t="s">
-        <v>678</v>
-      </c>
-      <c r="F323" t="s">
-        <v>676</v>
+        <v>568</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C323" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D323" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E323" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="F323" s="4" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B324" t="s">
         <v>676</v>
@@ -9023,7 +9027,7 @@
         <v>677</v>
       </c>
       <c r="E324" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F324" t="s">
         <v>676</v>
@@ -9031,7 +9035,7 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B325" t="s">
         <v>676</v>
@@ -9043,7 +9047,7 @@
         <v>677</v>
       </c>
       <c r="E325" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F325" t="s">
         <v>676</v>
@@ -9051,7 +9055,7 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B326" t="s">
         <v>676</v>
@@ -9063,7 +9067,7 @@
         <v>677</v>
       </c>
       <c r="E326" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F326" t="s">
         <v>676</v>
@@ -9071,7 +9075,7 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B327" t="s">
         <v>676</v>
@@ -9083,7 +9087,7 @@
         <v>677</v>
       </c>
       <c r="E327" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F327" t="s">
         <v>676</v>
@@ -9091,7 +9095,7 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B328" t="s">
         <v>676</v>
@@ -9103,7 +9107,7 @@
         <v>677</v>
       </c>
       <c r="E328" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F328" t="s">
         <v>676</v>
@@ -9111,7 +9115,7 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B329" t="s">
         <v>676</v>
@@ -9123,7 +9127,7 @@
         <v>677</v>
       </c>
       <c r="E329" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="F329" t="s">
         <v>676</v>
@@ -9131,7 +9135,7 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B330" t="s">
         <v>676</v>
@@ -9143,7 +9147,7 @@
         <v>677</v>
       </c>
       <c r="E330" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F330" t="s">
         <v>676</v>
@@ -9151,7 +9155,7 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B331" t="s">
         <v>676</v>
@@ -9163,7 +9167,7 @@
         <v>677</v>
       </c>
       <c r="E331" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F331" t="s">
         <v>676</v>
@@ -9171,7 +9175,7 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B332" t="s">
         <v>676</v>
@@ -9183,7 +9187,7 @@
         <v>677</v>
       </c>
       <c r="E332" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F332" t="s">
         <v>676</v>
@@ -9191,7 +9195,7 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B333" t="s">
         <v>676</v>
@@ -9203,7 +9207,7 @@
         <v>677</v>
       </c>
       <c r="E333" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="F333" t="s">
         <v>676</v>
@@ -9211,7 +9215,7 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B334" t="s">
         <v>676</v>
@@ -9223,7 +9227,7 @@
         <v>677</v>
       </c>
       <c r="E334" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F334" t="s">
         <v>676</v>
@@ -9231,7 +9235,7 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B335" t="s">
         <v>676</v>
@@ -9243,7 +9247,7 @@
         <v>677</v>
       </c>
       <c r="E335" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F335" t="s">
         <v>676</v>
@@ -9251,7 +9255,7 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B336" t="s">
         <v>676</v>
@@ -9263,9 +9267,29 @@
         <v>677</v>
       </c>
       <c r="E336" t="s">
+        <v>690</v>
+      </c>
+      <c r="F336" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A337" t="s">
+        <v>705</v>
+      </c>
+      <c r="B337" t="s">
+        <v>676</v>
+      </c>
+      <c r="C337" t="s">
+        <v>676</v>
+      </c>
+      <c r="D337" t="s">
+        <v>677</v>
+      </c>
+      <c r="E337" t="s">
         <v>691</v>
       </c>
-      <c r="F336" t="s">
+      <c r="F337" t="s">
         <v>676</v>
       </c>
     </row>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Library/CloudStorage/GoogleDrive-mvilla@buenavistacapital.com/.shortcut-targets-by-id/1Lbjcks5sDTC17AftNR6mDxW8bwAA7EaA/BVC/Analisis Portafolios/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17CCF183-43B9-9B44-A626-C29298E842B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A787CD-139D-DC49-AB78-BD200D21232B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60000" yWindow="-4060" windowWidth="21600" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15975,7 +15975,7 @@
         <v>699</v>
       </c>
       <c r="D484" t="s">
-        <v>995</v>
+        <v>7</v>
       </c>
       <c r="E484" t="s">
         <v>1072</v>
@@ -16695,7 +16695,7 @@
         <v>700</v>
       </c>
       <c r="D520" t="s">
-        <v>995</v>
+        <v>7</v>
       </c>
       <c r="E520" t="s">
         <v>1443</v>
@@ -16715,7 +16715,7 @@
         <v>700</v>
       </c>
       <c r="D521" t="s">
-        <v>995</v>
+        <v>7</v>
       </c>
       <c r="E521" t="s">
         <v>1445</v>
@@ -17215,7 +17215,7 @@
         <v>700</v>
       </c>
       <c r="D546" t="s">
-        <v>995</v>
+        <v>7</v>
       </c>
       <c r="E546" t="s">
         <v>1590</v>
@@ -17235,7 +17235,7 @@
         <v>700</v>
       </c>
       <c r="D547" t="s">
-        <v>995</v>
+        <v>7</v>
       </c>
       <c r="E547" t="s">
         <v>1593</v>
@@ -17655,7 +17655,7 @@
         <v>700</v>
       </c>
       <c r="D568" t="s">
-        <v>995</v>
+        <v>7</v>
       </c>
       <c r="E568" t="s">
         <v>1663</v>
@@ -17715,7 +17715,7 @@
         <v>700</v>
       </c>
       <c r="D571" t="s">
-        <v>995</v>
+        <v>7</v>
       </c>
       <c r="E571" t="s">
         <v>1669</v>
@@ -17735,7 +17735,7 @@
         <v>700</v>
       </c>
       <c r="D572" t="s">
-        <v>995</v>
+        <v>7</v>
       </c>
       <c r="E572" t="s">
         <v>1672</v>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A787CD-139D-DC49-AB78-BD200D21232B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1DF428-DFBB-C641-B78A-5E5E844E57BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15941,7 +15941,7 @@
         <v>1015</v>
       </c>
       <c r="F482" t="s">
-        <v>1016</v>
+        <v>658</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.2">
@@ -15961,7 +15961,7 @@
         <v>1038</v>
       </c>
       <c r="F483" t="s">
-        <v>1016</v>
+        <v>658</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.2">

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1DF428-DFBB-C641-B78A-5E5E844E57BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3057EEC-C825-8C41-88D3-68ADC0806C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$A$1:$I$621</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$598</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$606</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8516" uniqueCount="1968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8560" uniqueCount="1981">
   <si>
     <t>Ticker</t>
   </si>
@@ -5942,6 +5942,45 @@
   </si>
   <si>
     <t>NCWNUnited States ID EQUITY</t>
+  </si>
+  <si>
+    <t>QUEST RENTA LOCAL FONDO DE INVERSION</t>
+  </si>
+  <si>
+    <t>FALCOM CHILEAN FIXED INCOME</t>
+  </si>
+  <si>
+    <t>CREDICORP DEUDA CORPORATIVA</t>
+  </si>
+  <si>
+    <t>MONEDA DEUDA CHILE</t>
+  </si>
+  <si>
+    <t>LARRAIN VIAL DEUDA CORPORATIVA</t>
+  </si>
+  <si>
+    <t>ETF SINGULAR CHILE CORPORATIVO</t>
+  </si>
+  <si>
+    <t>MBI DEUDA TOTAL FONDO DE INVERION A</t>
+  </si>
+  <si>
+    <t>MBIDTANV CI EQUITY</t>
+  </si>
+  <si>
+    <t>FIQRLSA CI EQUITY</t>
+  </si>
+  <si>
+    <t>FCFIANV CI EQUITY</t>
+  </si>
+  <si>
+    <t>MODECHD CI EQUITY</t>
+  </si>
+  <si>
+    <t>DEUCORP CI EQUITY</t>
+  </si>
+  <si>
+    <t>CFIETFCC CC EQUITY</t>
   </si>
 </sst>
 </file>
@@ -6079,7 +6118,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6109,6 +6148,7 @@
     <xf numFmtId="10" fontId="8" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6415,7 +6455,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F598"/>
+  <dimension ref="A1:F606"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.33203125" bestFit="1" customWidth="1"/>
@@ -18264,8 +18304,156 @@
         <v>662</v>
       </c>
     </row>
+    <row r="599" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A599" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B599" t="s">
+        <v>700</v>
+      </c>
+      <c r="C599" t="s">
+        <v>700</v>
+      </c>
+      <c r="D599" t="s">
+        <v>663</v>
+      </c>
+      <c r="E599" s="11" t="s">
+        <v>1968</v>
+      </c>
+      <c r="F599" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="600" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A600" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B600" t="s">
+        <v>700</v>
+      </c>
+      <c r="C600" t="s">
+        <v>700</v>
+      </c>
+      <c r="D600" t="s">
+        <v>663</v>
+      </c>
+      <c r="E600" s="11" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F600" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="601" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A601" t="s">
+        <v>309</v>
+      </c>
+      <c r="B601" t="s">
+        <v>700</v>
+      </c>
+      <c r="C601" t="s">
+        <v>700</v>
+      </c>
+      <c r="D601" t="s">
+        <v>663</v>
+      </c>
+      <c r="E601" s="11" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F601" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="602" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A602" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B602" t="s">
+        <v>700</v>
+      </c>
+      <c r="C602" t="s">
+        <v>700</v>
+      </c>
+      <c r="D602" t="s">
+        <v>663</v>
+      </c>
+      <c r="E602" s="11" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F602" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="603" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A603" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B603" t="s">
+        <v>700</v>
+      </c>
+      <c r="C603" t="s">
+        <v>700</v>
+      </c>
+      <c r="D603" t="s">
+        <v>663</v>
+      </c>
+      <c r="E603" s="11" t="s">
+        <v>1972</v>
+      </c>
+      <c r="F603" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="604" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A604" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B604" t="s">
+        <v>700</v>
+      </c>
+      <c r="C604" t="s">
+        <v>700</v>
+      </c>
+      <c r="D604" t="s">
+        <v>663</v>
+      </c>
+      <c r="E604" s="11" t="s">
+        <v>1973</v>
+      </c>
+      <c r="F604" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="605" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A605" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B605" t="s">
+        <v>700</v>
+      </c>
+      <c r="C605" t="s">
+        <v>700</v>
+      </c>
+      <c r="D605" t="s">
+        <v>663</v>
+      </c>
+      <c r="E605" s="11" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F605" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="606" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D606" t="s">
+        <v>663</v>
+      </c>
+      <c r="F606" t="s">
+        <v>663</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F598" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F606" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3057EEC-C825-8C41-88D3-68ADC0806C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522F8C38-B1C3-4340-BA4D-0D4190E56C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8560" uniqueCount="1981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8558" uniqueCount="1981">
   <si>
     <t>Ticker</t>
   </si>
@@ -6118,7 +6118,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6148,7 +6148,6 @@
     <xf numFmtId="10" fontId="8" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6455,7 +6454,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F606"/>
+  <dimension ref="A1:F605"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.33203125" bestFit="1" customWidth="1"/>
@@ -18317,7 +18316,7 @@
       <c r="D599" t="s">
         <v>663</v>
       </c>
-      <c r="E599" s="11" t="s">
+      <c r="E599" t="s">
         <v>1968</v>
       </c>
       <c r="F599" t="s">
@@ -18337,7 +18336,7 @@
       <c r="D600" t="s">
         <v>663</v>
       </c>
-      <c r="E600" s="11" t="s">
+      <c r="E600" t="s">
         <v>1969</v>
       </c>
       <c r="F600" t="s">
@@ -18357,7 +18356,7 @@
       <c r="D601" t="s">
         <v>663</v>
       </c>
-      <c r="E601" s="11" t="s">
+      <c r="E601" t="s">
         <v>1970</v>
       </c>
       <c r="F601" t="s">
@@ -18377,7 +18376,7 @@
       <c r="D602" t="s">
         <v>663</v>
       </c>
-      <c r="E602" s="11" t="s">
+      <c r="E602" t="s">
         <v>1971</v>
       </c>
       <c r="F602" t="s">
@@ -18397,7 +18396,7 @@
       <c r="D603" t="s">
         <v>663</v>
       </c>
-      <c r="E603" s="11" t="s">
+      <c r="E603" t="s">
         <v>1972</v>
       </c>
       <c r="F603" t="s">
@@ -18417,7 +18416,7 @@
       <c r="D604" t="s">
         <v>663</v>
       </c>
-      <c r="E604" s="11" t="s">
+      <c r="E604" t="s">
         <v>1973</v>
       </c>
       <c r="F604" t="s">
@@ -18437,18 +18436,10 @@
       <c r="D605" t="s">
         <v>663</v>
       </c>
-      <c r="E605" s="11" t="s">
+      <c r="E605" t="s">
         <v>1974</v>
       </c>
       <c r="F605" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D606" t="s">
-        <v>663</v>
-      </c>
-      <c r="F606" t="s">
         <v>663</v>
       </c>
     </row>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522F8C38-B1C3-4340-BA4D-0D4190E56C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56163FE-B492-9D4C-A711-6822654074FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18320,7 +18320,7 @@
         <v>1968</v>
       </c>
       <c r="F599" t="s">
-        <v>663</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.2">
@@ -18340,7 +18340,7 @@
         <v>1969</v>
       </c>
       <c r="F600" t="s">
-        <v>663</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.2">
@@ -18360,7 +18360,7 @@
         <v>1970</v>
       </c>
       <c r="F601" t="s">
-        <v>663</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.2">
@@ -18380,7 +18380,7 @@
         <v>1971</v>
       </c>
       <c r="F602" t="s">
-        <v>663</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.2">
@@ -18400,7 +18400,7 @@
         <v>1972</v>
       </c>
       <c r="F603" t="s">
-        <v>663</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.2">
@@ -18420,7 +18420,7 @@
         <v>1973</v>
       </c>
       <c r="F604" t="s">
-        <v>663</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.2">
@@ -18440,7 +18440,7 @@
         <v>1974</v>
       </c>
       <c r="F605" t="s">
-        <v>663</v>
+        <v>1128</v>
       </c>
     </row>
   </sheetData>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56163FE-B492-9D4C-A711-6822654074FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E621D4D0-B4CB-7A42-96B4-7A9DA76E6F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E621D4D0-B4CB-7A42-96B4-7A9DA76E6F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E807050-482F-1F48-9177-F3E7B8C70071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8558" uniqueCount="1981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8558" uniqueCount="1982">
   <si>
     <t>Ticker</t>
   </si>
@@ -5965,22 +5965,25 @@
     <t>MBI DEUDA TOTAL FONDO DE INVERION A</t>
   </si>
   <si>
-    <t>MBIDTANV CI EQUITY</t>
-  </si>
-  <si>
-    <t>FIQRLSA CI EQUITY</t>
-  </si>
-  <si>
-    <t>FCFIANV CI EQUITY</t>
-  </si>
-  <si>
-    <t>MODECHD CI EQUITY</t>
-  </si>
-  <si>
-    <t>DEUCORP CI EQUITY</t>
-  </si>
-  <si>
-    <t>CFIETFCC CC EQUITY</t>
+    <t>FIQRLSA CI Equity</t>
+  </si>
+  <si>
+    <t>FCFIANV CI Equity</t>
+  </si>
+  <si>
+    <t>IMTDECI CI Equity</t>
+  </si>
+  <si>
+    <t>MODECHD CI Equity</t>
+  </si>
+  <si>
+    <t>DEUCORP CI Equity</t>
+  </si>
+  <si>
+    <t>CFIETFCC CC Equity</t>
+  </si>
+  <si>
+    <t>MBIDTANV CI Equity</t>
   </si>
 </sst>
 </file>
@@ -18305,7 +18308,7 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B599" t="s">
         <v>700</v>
@@ -18325,7 +18328,7 @@
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="B600" t="s">
         <v>700</v>
@@ -18345,7 +18348,7 @@
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
-        <v>309</v>
+        <v>1977</v>
       </c>
       <c r="B601" t="s">
         <v>700</v>
@@ -18425,7 +18428,7 @@
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
-        <v>1975</v>
+        <v>1981</v>
       </c>
       <c r="B605" t="s">
         <v>700</v>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E807050-482F-1F48-9177-F3E7B8C70071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E272B2-221C-5143-AEE1-4D7947229B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E272B2-221C-5143-AEE1-4D7947229B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CE0EB2-1EAD-4449-8F4C-26889F067EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8558" uniqueCount="1982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8630" uniqueCount="2007">
   <si>
     <t>Ticker</t>
   </si>
@@ -5984,6 +5984,81 @@
   </si>
   <si>
     <t>MBIDTANV CI Equity</t>
+  </si>
+  <si>
+    <t>IEMJXUS LX EQUITY</t>
+  </si>
+  <si>
+    <t>MLWORHD LX EQUITY</t>
+  </si>
+  <si>
+    <t>POLGTIU ID Equity</t>
+  </si>
+  <si>
+    <t>NINETY ONE GLOBAL STRATEGY FUND - EMERGING MARKETS EQUITY FUNDS</t>
+  </si>
+  <si>
+    <t>BLACKROCK GLOBAL FUNDS - WORLD HEALTHSCIENCE FUND</t>
+  </si>
+  <si>
+    <t>POLAR CAPITAL FUNDS PLC - GLOBAL TECHNOLOGY FUND</t>
+  </si>
+  <si>
+    <t>EEM US Equity</t>
+  </si>
+  <si>
+    <t>XMME GR Equity</t>
+  </si>
+  <si>
+    <t>AEMD GR Equity</t>
+  </si>
+  <si>
+    <t>EMMUKD SW Equity</t>
+  </si>
+  <si>
+    <t>HMEM LN EQUITY</t>
+  </si>
+  <si>
+    <t>JRMD LN Equity</t>
+  </si>
+  <si>
+    <t>ZEM CN Equity</t>
+  </si>
+  <si>
+    <t>MXFS LN EQUITY</t>
+  </si>
+  <si>
+    <t>2520 JP Equity</t>
+  </si>
+  <si>
+    <t>ISHARES MSCI POLAND ETF</t>
+  </si>
+  <si>
+    <t>ISHARES MSCI EMERGIN MARKETS ETF</t>
+  </si>
+  <si>
+    <t>XTRACKERS MSCI EMERGIN MARKETS UCITS ETF</t>
+  </si>
+  <si>
+    <t>AMUNDI CORE MSCI EMERGING MARKETS UCITS ETF</t>
+  </si>
+  <si>
+    <t>UBS CORE MSCI EM UCITS ETF</t>
+  </si>
+  <si>
+    <t>HSBC MSCI EMERGING MARKETS UCITS ETF</t>
+  </si>
+  <si>
+    <t>JPMORGAN GLOBAL EMERGING MARKETS RESEARCH ENHANCED</t>
+  </si>
+  <si>
+    <t>BMO MSCI EMERGING MARKETS INDEX ETF</t>
+  </si>
+  <si>
+    <t>INVESCO MSCI EMERGING MARKETS UCITS ETF</t>
+  </si>
+  <si>
+    <t>NEXT FUNDS EMERGIN MARKET EQUITY MSCI-EM (UNHEDGED)</t>
   </si>
 </sst>
 </file>
@@ -6457,7 +6532,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F605"/>
+  <dimension ref="A1:F617"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.33203125" bestFit="1" customWidth="1"/>
@@ -16960,7 +17035,7 @@
         <v>17</v>
       </c>
       <c r="E531" t="s">
-        <v>1541</v>
+        <v>1997</v>
       </c>
       <c r="F531" t="s">
         <v>1128</v>
@@ -18443,6 +18518,246 @@
         <v>1974</v>
       </c>
       <c r="F605" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="606" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A606" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B606" t="s">
+        <v>699</v>
+      </c>
+      <c r="C606" t="s">
+        <v>699</v>
+      </c>
+      <c r="D606" t="s">
+        <v>20</v>
+      </c>
+      <c r="E606" t="s">
+        <v>1985</v>
+      </c>
+      <c r="F606" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="607" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A607" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B607" t="s">
+        <v>699</v>
+      </c>
+      <c r="C607" t="s">
+        <v>699</v>
+      </c>
+      <c r="D607" t="s">
+        <v>65</v>
+      </c>
+      <c r="E607" t="s">
+        <v>1986</v>
+      </c>
+      <c r="F607" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="608" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A608" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B608" t="s">
+        <v>699</v>
+      </c>
+      <c r="C608" t="s">
+        <v>699</v>
+      </c>
+      <c r="D608" t="s">
+        <v>65</v>
+      </c>
+      <c r="E608" t="s">
+        <v>1987</v>
+      </c>
+      <c r="F608" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="609" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A609" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B609" t="s">
+        <v>699</v>
+      </c>
+      <c r="C609" t="s">
+        <v>699</v>
+      </c>
+      <c r="D609" t="s">
+        <v>65</v>
+      </c>
+      <c r="E609" t="s">
+        <v>1998</v>
+      </c>
+      <c r="F609" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="610" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A610" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B610" t="s">
+        <v>699</v>
+      </c>
+      <c r="C610" t="s">
+        <v>699</v>
+      </c>
+      <c r="D610" t="s">
+        <v>65</v>
+      </c>
+      <c r="E610" t="s">
+        <v>1999</v>
+      </c>
+      <c r="F610" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="611" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A611" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B611" t="s">
+        <v>699</v>
+      </c>
+      <c r="C611" t="s">
+        <v>699</v>
+      </c>
+      <c r="D611" t="s">
+        <v>65</v>
+      </c>
+      <c r="E611" t="s">
+        <v>2000</v>
+      </c>
+      <c r="F611" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="612" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A612" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B612" t="s">
+        <v>699</v>
+      </c>
+      <c r="C612" t="s">
+        <v>699</v>
+      </c>
+      <c r="D612" t="s">
+        <v>65</v>
+      </c>
+      <c r="E612" t="s">
+        <v>2001</v>
+      </c>
+      <c r="F612" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="613" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A613" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B613" t="s">
+        <v>699</v>
+      </c>
+      <c r="C613" t="s">
+        <v>699</v>
+      </c>
+      <c r="D613" t="s">
+        <v>65</v>
+      </c>
+      <c r="E613" t="s">
+        <v>2002</v>
+      </c>
+      <c r="F613" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="614" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A614" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B614" t="s">
+        <v>699</v>
+      </c>
+      <c r="C614" t="s">
+        <v>699</v>
+      </c>
+      <c r="D614" t="s">
+        <v>65</v>
+      </c>
+      <c r="E614" t="s">
+        <v>2003</v>
+      </c>
+      <c r="F614" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="615" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A615" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B615" t="s">
+        <v>699</v>
+      </c>
+      <c r="C615" t="s">
+        <v>699</v>
+      </c>
+      <c r="D615" t="s">
+        <v>65</v>
+      </c>
+      <c r="E615" t="s">
+        <v>2004</v>
+      </c>
+      <c r="F615" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="616" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A616" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B616" t="s">
+        <v>699</v>
+      </c>
+      <c r="C616" t="s">
+        <v>699</v>
+      </c>
+      <c r="D616" t="s">
+        <v>65</v>
+      </c>
+      <c r="E616" t="s">
+        <v>2005</v>
+      </c>
+      <c r="F616" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="617" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A617" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B617" t="s">
+        <v>699</v>
+      </c>
+      <c r="C617" t="s">
+        <v>699</v>
+      </c>
+      <c r="D617" t="s">
+        <v>65</v>
+      </c>
+      <c r="E617" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F617" t="s">
         <v>1128</v>
       </c>
     </row>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CE0EB2-1EAD-4449-8F4C-26889F067EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C18764-B3EE-0C4E-9FF3-F85F9226F537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C18764-B3EE-0C4E-9FF3-F85F9226F537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1291918-73C2-4D44-B43E-83CACE374289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18552,7 +18552,7 @@
         <v>699</v>
       </c>
       <c r="D607" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E607" t="s">
         <v>1986</v>
@@ -18572,7 +18572,7 @@
         <v>699</v>
       </c>
       <c r="D608" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E608" t="s">
         <v>1987</v>
@@ -18592,7 +18592,7 @@
         <v>699</v>
       </c>
       <c r="D609" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E609" t="s">
         <v>1998</v>
@@ -18612,7 +18612,7 @@
         <v>699</v>
       </c>
       <c r="D610" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E610" t="s">
         <v>1999</v>
@@ -18632,7 +18632,7 @@
         <v>699</v>
       </c>
       <c r="D611" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E611" t="s">
         <v>2000</v>
@@ -18652,7 +18652,7 @@
         <v>699</v>
       </c>
       <c r="D612" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E612" t="s">
         <v>2001</v>
@@ -18672,7 +18672,7 @@
         <v>699</v>
       </c>
       <c r="D613" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E613" t="s">
         <v>2002</v>
@@ -18692,7 +18692,7 @@
         <v>699</v>
       </c>
       <c r="D614" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E614" t="s">
         <v>2003</v>
@@ -18712,7 +18712,7 @@
         <v>699</v>
       </c>
       <c r="D615" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E615" t="s">
         <v>2004</v>
@@ -18732,7 +18732,7 @@
         <v>699</v>
       </c>
       <c r="D616" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E616" t="s">
         <v>2005</v>
@@ -18752,7 +18752,7 @@
         <v>699</v>
       </c>
       <c r="D617" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E617" t="s">
         <v>2006</v>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1291918-73C2-4D44-B43E-83CACE374289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB456722-B2B4-A249-BE2D-0AAD97288E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18552,7 +18552,7 @@
         <v>699</v>
       </c>
       <c r="D607" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E607" t="s">
         <v>1986</v>
@@ -18572,7 +18572,7 @@
         <v>699</v>
       </c>
       <c r="D608" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E608" t="s">
         <v>1987</v>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB456722-B2B4-A249-BE2D-0AAD97288E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B034C07-EDEA-D849-9368-6A459D8A08AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8630" uniqueCount="2007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8630" uniqueCount="2008">
   <si>
     <t>Ticker</t>
   </si>
@@ -6059,6 +6059,9 @@
   </si>
   <si>
     <t>NEXT FUNDS EMERGIN MARKET EQUITY MSCI-EM (UNHEDGED)</t>
+  </si>
+  <si>
+    <t>MRCLPAE CI EQUITY</t>
   </si>
 </sst>
 </file>
@@ -11063,7 +11066,7 @@
     </row>
     <row r="227" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>459</v>
+        <v>2007</v>
       </c>
       <c r="B227" t="s">
         <v>700</v>
@@ -24868,9 +24871,9 @@
       </c>
     </row>
     <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A204" t="str">
+      <c r="A204" t="e">
         <f>VLOOKUP(B204,Sheet1!$A$1:$B$415,1,FALSE)</f>
-        <v>MRCLP CI EQUITY</v>
+        <v>#N/A</v>
       </c>
       <c r="B204" t="s">
         <v>459</v>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B034C07-EDEA-D849-9368-6A459D8A08AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF61BBF8-3879-E74A-9084-E045198D5EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8630" uniqueCount="2008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8672" uniqueCount="2022">
   <si>
     <t>Ticker</t>
   </si>
@@ -6062,6 +6062,48 @@
   </si>
   <si>
     <t>MRCLPAE CI EQUITY</t>
+  </si>
+  <si>
+    <t>CFIMRCLP CI EQUITY</t>
+  </si>
+  <si>
+    <t>MONEDA RENTA CLP SERIE A</t>
+  </si>
+  <si>
+    <t>SECRNOM CI EQUITY</t>
+  </si>
+  <si>
+    <t>FONDO DE INVERSION SECURITY HY CHILE</t>
+  </si>
+  <si>
+    <t>SECR1NV CI EQUITY</t>
+  </si>
+  <si>
+    <t>FONDO DE INVERSION SECURITY RENTA FIJA NACIONAL</t>
+  </si>
+  <si>
+    <t>FILRDCM CI EQUITY</t>
+  </si>
+  <si>
+    <t>FONDO DE INVERSION LARRAINVIAL DEUDA CHILE</t>
+  </si>
+  <si>
+    <t>FALCDCW CI EQUITY</t>
+  </si>
+  <si>
+    <t>FALCOM DEUDA CORPORATIVA CHILE</t>
+  </si>
+  <si>
+    <t>IMTSCLD CI EQUITY</t>
+  </si>
+  <si>
+    <t>FONDO DE INVERSION CREDICORP CAPITAL SPREAD CORPORATIVO LOCAL</t>
+  </si>
+  <si>
+    <t>FYDCLAC CI EQUITY</t>
+  </si>
+  <si>
+    <t>FONDO DE INVERSION LARRAINVIAL ENFOQUE</t>
   </si>
 </sst>
 </file>
@@ -6535,7 +6577,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F617"/>
+  <dimension ref="A1:F624"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.33203125" bestFit="1" customWidth="1"/>
@@ -18761,6 +18803,146 @@
         <v>2006</v>
       </c>
       <c r="F617" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="618" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A618" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B618" t="s">
+        <v>700</v>
+      </c>
+      <c r="C618" t="s">
+        <v>700</v>
+      </c>
+      <c r="D618" t="s">
+        <v>663</v>
+      </c>
+      <c r="E618" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F618" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="619" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A619" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B619" t="s">
+        <v>700</v>
+      </c>
+      <c r="C619" t="s">
+        <v>700</v>
+      </c>
+      <c r="D619" t="s">
+        <v>663</v>
+      </c>
+      <c r="E619" t="s">
+        <v>2011</v>
+      </c>
+      <c r="F619" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="620" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A620" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B620" t="s">
+        <v>700</v>
+      </c>
+      <c r="C620" t="s">
+        <v>700</v>
+      </c>
+      <c r="D620" t="s">
+        <v>663</v>
+      </c>
+      <c r="E620" t="s">
+        <v>2013</v>
+      </c>
+      <c r="F620" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="621" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A621" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B621" t="s">
+        <v>700</v>
+      </c>
+      <c r="C621" t="s">
+        <v>700</v>
+      </c>
+      <c r="D621" t="s">
+        <v>663</v>
+      </c>
+      <c r="E621" t="s">
+        <v>2015</v>
+      </c>
+      <c r="F621" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="622" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A622" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B622" t="s">
+        <v>700</v>
+      </c>
+      <c r="C622" t="s">
+        <v>700</v>
+      </c>
+      <c r="D622" t="s">
+        <v>663</v>
+      </c>
+      <c r="E622" t="s">
+        <v>2017</v>
+      </c>
+      <c r="F622" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="623" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A623" t="s">
+        <v>2018</v>
+      </c>
+      <c r="B623" t="s">
+        <v>700</v>
+      </c>
+      <c r="C623" t="s">
+        <v>700</v>
+      </c>
+      <c r="D623" t="s">
+        <v>663</v>
+      </c>
+      <c r="E623" t="s">
+        <v>2019</v>
+      </c>
+      <c r="F623" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="624" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A624" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B624" t="s">
+        <v>700</v>
+      </c>
+      <c r="C624" t="s">
+        <v>700</v>
+      </c>
+      <c r="D624" t="s">
+        <v>663</v>
+      </c>
+      <c r="E624" t="s">
+        <v>2021</v>
+      </c>
+      <c r="F624" t="s">
         <v>1128</v>
       </c>
     </row>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF61BBF8-3879-E74A-9084-E045198D5EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2F1EDD-CBB1-9148-88D5-938DBB08FE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18931,10 +18931,10 @@
         <v>2020</v>
       </c>
       <c r="B624" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C624" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D624" t="s">
         <v>663</v>

--- a/dict_temp_full_portfolio.xlsx
+++ b/dict_temp_full_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matias/Desktop/Proyectos/ranking-fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2F1EDD-CBB1-9148-88D5-938DBB08FE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBFC7F7-09C3-9E43-BB2E-D76372E1283C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32160" yWindow="500" windowWidth="30240" windowHeight="17800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6103,7 +6103,7 @@
     <t>FYDCLAC CI EQUITY</t>
   </si>
   <si>
-    <t>FONDO DE INVERSION LARRAINVIAL ENFOQUE</t>
+    <t>FYNSA DEUDA CHILE A</t>
   </si>
 </sst>
 </file>
@@ -18931,10 +18931,10 @@
         <v>2020</v>
       </c>
       <c r="B624" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C624" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D624" t="s">
         <v>663</v>
